--- a/artfynd/A 7132-2026 artfynd.xlsx
+++ b/artfynd/A 7132-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113209831</v>
+        <v>87796007</v>
       </c>
       <c r="B2" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>1001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Flytsvalting</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Luronium natans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) Raf.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kushult 2, Hl</t>
+          <t>Svarten, vid bryggor NV Kushult, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>355270</v>
+        <v>355268</v>
       </c>
       <c r="R2" t="n">
-        <v>6336462</v>
+        <v>6336585</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Enstaka blommande exemplar. Antal skattat utifrån det som kunde ses från strand och bryggor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,72 +775,75 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Lars Stibe</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Lars Stibe</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113209828</v>
+        <v>87796217</v>
       </c>
       <c r="B3" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flytsvalting</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Luronium natans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Raf.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kushult 2, Hl</t>
+          <t>Svarten, NNV Kushult, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>355270</v>
+        <v>355325</v>
       </c>
       <c r="R3" t="n">
-        <v>6336462</v>
+        <v>6336685</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,21 +881,571 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Lars Stibe</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Stibe</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87882356</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98683</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Flytsvalting</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Luronium natans</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Raf.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svarten, vid bryggor NV Kushult, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>355266</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6336578</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rolfstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-09-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-09-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulf Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulf Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94837789</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98683</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Flytsvalting</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Luronium natans</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Raf.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svarten, vid bryggor NV Kushult, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>355256</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6336584</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rolfstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fanns säkert mer, men detta noterat direkt v om bryggan.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pav Johnsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pav Johnsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112143500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98683</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flytsvalting</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Luronium natans</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Raf.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svarten (25) N Kushult, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>355277</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6336586</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rolfstorp</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>N-Var-0954-biogeo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Arne Lysell, Lars Stibe, Lars-Erik Magnusson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113209828</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kushult 2, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>355270</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6336462</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rolfstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Niklas Lönnell</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Niklas Lönnell</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113209831</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kushult 2, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>355270</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6336462</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rolfstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
